--- a/光伏配储项目/电价数据/2026/陂美站.xlsx
+++ b/光伏配储项目/电价数据/2026/陂美站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.3355</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.98739</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.4084100000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.26402</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.29097</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.25746</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.27323</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.25906</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.27457</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07208000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.22946</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.16978</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25108</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25571</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24036</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.19288</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.28572</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.28599</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.29765</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.69186</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.6632100000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.88293</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.55526</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.4311</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.48318</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4986</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.7740199999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.18381</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.57912</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.5958</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.60189</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.40348</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.63948</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.79863</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.5870700000000001</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.91901</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.00238</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.50712</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.11357</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.02647</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.96753</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.62185</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.56632</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.54545</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.47785</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.49148</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.77715</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.01167</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.07039</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48234</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.50561</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49292</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49175</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47143</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.45481</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.43108</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.41877</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37343</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45639</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.42106</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.64612</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.60777</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.75334</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.25301</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.56694</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.4834</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.39679</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.61222</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.85864</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.58736</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.71793</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7476699999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.39178</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.42306</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.94829</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.56661</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.40588</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.63122</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.24148</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.3906</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7177</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.17994</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.97637</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.23855</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.10087</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.33529</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.98223</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44005</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.95156</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.95797</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44006</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33396</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.47585</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48464</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.43594</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43329</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46101</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.43819</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.42961</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.15896</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.20126</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26832</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.70235</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.5934299999999999</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.58368</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.7733099999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.7733300000000001</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.7514299999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.78974</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.8438600000000001</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.9087799999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.93616</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.02199</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.51498</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5377999999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.75183</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.76585</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.63607</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.63374</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.50012</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.6436499999999999</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45811</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51125</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52074</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.58594</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.62798</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.6043999999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.63814</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.11177</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.59572</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.7089099999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46096</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51071</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5888300000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.68389</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7247899999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.80243</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.44388</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.62309</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.50343</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.5647000000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.7171799999999999</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5482899999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7748400000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.64807</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5904299999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5411900000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.7066699999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43233</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.44831</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39279</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34114</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.56863</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.54323</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.47016</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39891</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40405</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.40069</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47878</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.43241</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.45454</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44649</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.46654</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.54786</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48461</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46907</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21003</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.81008</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.50048</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.45224</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41012</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.25437</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.5175700000000001</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.41408</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.41652</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.42473</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.49884</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.5774900000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.44145</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.67289</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.47854</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.44481</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50241</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42584</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40774</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29226</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14358</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02791</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26454</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25776</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.23913</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10394</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.26727</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.04342</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26354</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.44392</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31967</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.25579</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.26001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.22785</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.20176</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.25638</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.14771</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25654</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.03433</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.16902</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25418</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.22363</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.20213</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.24829</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.18493</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25568</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27636</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.2115</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04518</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01026</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20666</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04949</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27609</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01383</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06081</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05902</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3172</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.26598</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42085</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.44402</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78413</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8704500000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.66314</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57563</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44658</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37563</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5321399999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60266</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.84772</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.5397999999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.7550800000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.6152799999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26842</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.49223</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29612</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18926</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26587</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26589</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.28011</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26597</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32571</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.19875</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.29121</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.25892</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.28679</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.26324</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.28428</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.25562</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.46239</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26172</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.18454</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27732</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.25748</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.28455</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.25293</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.24516</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.22057</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.20442</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.19892</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.2216</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.12634</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.21724</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.10331</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.19015</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.19186</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.17111</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.19606</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.27181</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.28167</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.23247</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.27849</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.26366</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27952</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.28063</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.25145</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.27474</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.25716</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.28229</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.29361</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.28889</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.28523</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.28056</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.29167</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.16573</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.6152799999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.20523</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.79101</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.51588</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.6266900000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.47871</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.18332</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.17069</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.28985</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.28822</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.27677</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.41319</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.13833</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.20992</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.20909</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.28582</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.20114</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.26702</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.40385</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.23357</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.28187</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.13305</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.24528</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.26816</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.2321</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.2014</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.28801</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26888</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.20668</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.22968</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.26277</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.24067</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.28797</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.21833</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.28673</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.2351</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.26801</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.26038</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.27045</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.42914</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.56149</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.25678</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.23529</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.26303</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.24342</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.23676</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.15578</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.18368</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19743</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.17671</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.19453</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.15212</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.22134</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.24096</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.23876</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.27301</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.26929</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.10977</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.11298</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.22141</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.23361</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.26501</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.02134</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.13259</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.20216</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.02251</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.16506</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.16195</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.18014</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.25466</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.27538</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.19374</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.26395</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.15788</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.2805299999999999</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.16707</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.26756</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.11837</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.17988</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.26255</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.25015</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.26068</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.2534</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.25538</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.26862</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.2641</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26983</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.26963</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.26967</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27653</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.28371</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.29621</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.47522</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25631</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28616</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29302</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28337</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28567</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29168</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.45869</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.42088</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.43358</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.55525</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.39045</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.40278</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.31507</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.29108</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29872</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29644</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.5405</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.55653</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.16177</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.49365</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.73695</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49567</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.46171</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.63164</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.7673300000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.50026</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.60199</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.92532</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27888</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.53371</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.42679</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.41895</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.17277</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.45289</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.61948</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.5770700000000001</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.56199</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.9168099999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.60222</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.58408</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.69345</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.5221699999999999</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.65338</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.41139</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.44343</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.8352000000000001</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.65632</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.5949800000000001</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.8334600000000001</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70343</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47895</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.18517</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.27177</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.23364</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28895</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.03731</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.17646</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.28741</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28332</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20754</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.1994</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27642</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.28108</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27779</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27562</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27557</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.2013</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19859</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.16422</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.24041</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19832</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20397</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.17039</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.21125</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17792</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16892</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.20904</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.23292</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.27901</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.28572</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.25977</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.2794700000000001</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.27742</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.24939</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.26458</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.27261</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.23827</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.25591</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.26238</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.16816</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.27996</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.28023</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27883</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28909</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27925</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.26973</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.23725</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.16288</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.13576</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.24135</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32087</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.00627</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27749</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28758</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27704</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27738</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27749</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28779</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27275</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.51091</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.98014</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.9743200000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.41435</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.21651</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29959</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28926</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.51068</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.46032</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.42512</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.67924</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.5077</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.06576</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.97949</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.06509</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.27591</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.5974700000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.5165</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.73793</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.54199</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.6789400000000001</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31737</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.29397</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45352</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.45168</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.43111</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.5214099999999999</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.5740299999999999</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.63874</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5842999999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40672</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40575</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.45904</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6750700000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40777</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.02189</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.50175</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.28749</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.36279</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.44912</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.92961</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.7158300000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6446499999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.32687</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40665</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39658</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27961</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29471</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.02417</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.28356</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.65843</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38259</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42632</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.43592</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.43112</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.43149</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.20845</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38698</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.20596</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.20291</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.22201</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.2606</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.24273</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.21035</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.17809</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.15416</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.18655</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.17825</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.1956</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.18863</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.26469</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.23566</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.22751</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.17938</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.02263</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.26515</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17959</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.008320000000000001</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.21002</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17842</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.01707</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.16842</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.17323</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.20579</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.17071</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.17358</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17645</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.01585</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17931</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.01565</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.00775</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.19081</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.19114</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.16048</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28557</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.01966</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.26316</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.18353</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.22983</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.18371</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29197</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.06681000000000001</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.29872</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00349</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26098</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.28399</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25591</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.28775</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.25891</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.26534</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28056</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.26309</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.27466</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.26421</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22997</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.22194</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.20781</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25523</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.25284</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.25772</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.25621</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.17836</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.18658</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.25795</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.16555</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.27588</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.16226</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.22277</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.23503</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.27848</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.27891</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28575</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27746</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.06077</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.19387</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.19078</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.00865</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20954</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22925</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.22131</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.05058</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.00193</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.01089</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.01088</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.01021</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.01021</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.01061</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.20426</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.00257</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.01021</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.01026</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.18517</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.00191</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.00192</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.01205</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.00364</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24653</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04404</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00549</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.12369</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02201</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01834</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02935</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04408</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00547</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27029</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04105</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03595</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03757</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.25917</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27608</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.28555</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28245</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30041</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27493</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.04956</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28887</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.18324</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17751</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.18203</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.17925</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.00792</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.17517</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.16342</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.006730000000000001</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.03808</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.03529</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.00992</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.00609</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.04167</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.02019</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.02282</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.20812</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28229</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.009779999999999999</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.2479</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.01315</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85972</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86148</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09423000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.01034</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25323</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29601</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.4326</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00216</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06858</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47484</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.98472</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.6682899999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.44741</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.5180399999999999</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.11805</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.2231</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.46403</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.78074</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.54476</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.03684</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03506</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.04144</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.18125</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.44979</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.54515</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.46501</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31274</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.04167</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.53637</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.27406</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.20589</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26566</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.26138</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25436</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.22455</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.27717</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.21285</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.18051</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20827</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.17469</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.17751</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.008410000000000001</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.17458</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.19616</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.24399</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.29851</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.25197</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.26195</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25888</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.28056</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25841</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30204</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41855</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.2966</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.73887</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.50213</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29686</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.5310199999999999</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.45973</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.53008</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.03223</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.10528</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.45977</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.45141</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.63205</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.9314600000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.08791</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.47755</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.8398099999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.43356</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43068</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20461</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.32051</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.44322</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42967</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41063</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.70853</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.76988</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.25072</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.82704</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.21067</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.6477999999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.8913300000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.7563200000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.54664</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.16152</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.0315</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.09317</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.9324199999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.76881</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.46984</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3251</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.008750000000000001</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28795</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.4379</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.58686</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.20139</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43627</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.5612200000000001</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.5900700000000001</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.43309</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.48247</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.59811</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48286</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.60811</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.8417899999999999</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.47369</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.63189</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.49833</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.53826</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32942</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9526</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.45584</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.55237</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.49656</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.48073</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.40824</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.5494</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.55344</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.7243200000000001</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.53012</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.4025899999999999</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.49355</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.51139</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.43658</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.34004</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17607</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14573</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19861</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14598</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28762</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04752</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12154</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22593</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26026</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14409</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14522</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18833</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26681</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15579</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.16275</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19956</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.20295</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.42051</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.42694</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39079</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3699</v>
       </c>
     </row>
   </sheetData>
